--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/17.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/17.xlsx
@@ -426,13 +426,13 @@
         <v>-10.65024163425561</v>
       </c>
       <c r="E2">
-        <v>-13.01592193408471</v>
+        <v>-13.5896423932852</v>
       </c>
       <c r="F2">
-        <v>1.71276791457907</v>
+        <v>-0.2731468430140195</v>
       </c>
       <c r="G2">
-        <v>-18.00065786018867</v>
+        <v>-18.90521037090546</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.93842042634825</v>
       </c>
       <c r="E3">
-        <v>-12.61645776244005</v>
+        <v>-13.93481993970302</v>
       </c>
       <c r="F3">
-        <v>1.492801577704884</v>
+        <v>-0.1304845805364859</v>
       </c>
       <c r="G3">
-        <v>-16.94274107458381</v>
+        <v>-18.37266807846559</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.10573454091208</v>
       </c>
       <c r="E4">
-        <v>-12.44037406190129</v>
+        <v>-14.55339508121166</v>
       </c>
       <c r="F4">
-        <v>1.782266282939143</v>
+        <v>-0.1998694625623753</v>
       </c>
       <c r="G4">
-        <v>-17.16184259290381</v>
+        <v>-17.75064773665448</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.274176935600977</v>
       </c>
       <c r="E5">
-        <v>-12.7646568021439</v>
+        <v>-15.11063559787523</v>
       </c>
       <c r="F5">
-        <v>2.088545189715427</v>
+        <v>-0.01443113577167794</v>
       </c>
       <c r="G5">
-        <v>-16.90461506594749</v>
+        <v>-17.59276165213461</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.462488957341033</v>
       </c>
       <c r="E6">
-        <v>-13.40799754278249</v>
+        <v>-14.37909726154258</v>
       </c>
       <c r="F6">
-        <v>1.592879957106704</v>
+        <v>0.5319119578055136</v>
       </c>
       <c r="G6">
-        <v>-15.69163571609805</v>
+        <v>-16.66016843913696</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.726606790789701</v>
       </c>
       <c r="E7">
-        <v>-15.39326162852981</v>
+        <v>-17.49534308921058</v>
       </c>
       <c r="F7">
-        <v>1.638127041382418</v>
+        <v>-0.01035639651730717</v>
       </c>
       <c r="G7">
-        <v>-16.06133934152872</v>
+        <v>-16.55663936237637</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.083063273245022</v>
       </c>
       <c r="E8">
-        <v>-14.10728619317785</v>
+        <v>-16.39972594172081</v>
       </c>
       <c r="F8">
-        <v>1.772824551282035</v>
+        <v>0.4152074162621052</v>
       </c>
       <c r="G8">
-        <v>-14.23861014944641</v>
+        <v>-15.99683698028838</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.551582125411819</v>
       </c>
       <c r="E9">
-        <v>-14.68794666850213</v>
+        <v>-18.00033205419648</v>
       </c>
       <c r="F9">
-        <v>2.334055063822339</v>
+        <v>0.461197546098131</v>
       </c>
       <c r="G9">
-        <v>-13.81434065668918</v>
+        <v>-15.33291027167302</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.13119868165762</v>
       </c>
       <c r="E10">
-        <v>-16.68073637317003</v>
+        <v>-18.32298673559976</v>
       </c>
       <c r="F10">
-        <v>2.480291731642952</v>
+        <v>0.9463623935089679</v>
       </c>
       <c r="G10">
-        <v>-13.71938918128268</v>
+        <v>-14.91694425208783</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.813078321247667</v>
       </c>
       <c r="E11">
-        <v>-16.21081712461099</v>
+        <v>-19.01998696655514</v>
       </c>
       <c r="F11">
-        <v>2.192573224893795</v>
+        <v>1.260172816711504</v>
       </c>
       <c r="G11">
-        <v>-13.11403974905813</v>
+        <v>-14.59044192277861</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.585632289548252</v>
       </c>
       <c r="E12">
-        <v>-17.59699293638576</v>
+        <v>-19.69561061882162</v>
       </c>
       <c r="F12">
-        <v>2.802743683591494</v>
+        <v>1.249907687856013</v>
       </c>
       <c r="G12">
-        <v>-12.11135065453369</v>
+        <v>-14.07889001685128</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.42275903241551</v>
       </c>
       <c r="E13">
-        <v>-18.06553747199629</v>
+        <v>-19.37897809383934</v>
       </c>
       <c r="F13">
-        <v>2.691838542235085</v>
+        <v>1.831484560543879</v>
       </c>
       <c r="G13">
-        <v>-12.40056241347574</v>
+        <v>-13.78592792330409</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.309748029000505</v>
       </c>
       <c r="E14">
-        <v>-19.52796624369492</v>
+        <v>-20.1151846397011</v>
       </c>
       <c r="F14">
-        <v>3.240346988203194</v>
+        <v>2.24435115777318</v>
       </c>
       <c r="G14">
-        <v>-11.27178740892347</v>
+        <v>-13.82627437021516</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.218747351578134</v>
       </c>
       <c r="E15">
-        <v>-20.22097939177846</v>
+        <v>-21.37513189968036</v>
       </c>
       <c r="F15">
-        <v>3.432775079138714</v>
+        <v>2.254011578424628</v>
       </c>
       <c r="G15">
-        <v>-12.26425282762912</v>
+        <v>-13.72095171192046</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.1319186437436</v>
       </c>
       <c r="E16">
-        <v>-20.93813931050455</v>
+        <v>-21.85389333514997</v>
       </c>
       <c r="F16">
-        <v>4.098868621199407</v>
+        <v>2.492248386734961</v>
       </c>
       <c r="G16">
-        <v>-10.22821666484679</v>
+        <v>-13.37918174824241</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.029952617408523</v>
       </c>
       <c r="E17">
-        <v>-20.62053908728359</v>
+        <v>-22.84330871585255</v>
       </c>
       <c r="F17">
-        <v>3.533678512473721</v>
+        <v>2.500894885685382</v>
       </c>
       <c r="G17">
-        <v>-10.73569319846739</v>
+        <v>-12.81987279688215</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.898586511650248</v>
       </c>
       <c r="E18">
-        <v>-22.62521943597448</v>
+        <v>-23.90348235789623</v>
       </c>
       <c r="F18">
-        <v>4.265612352443725</v>
+        <v>2.897030118112939</v>
       </c>
       <c r="G18">
-        <v>-10.24215804096333</v>
+        <v>-13.50033857248221</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.730786568428789</v>
       </c>
       <c r="E19">
-        <v>-23.00550407772108</v>
+        <v>-24.68074755091524</v>
       </c>
       <c r="F19">
-        <v>4.002227966519206</v>
+        <v>3.419832666837374</v>
       </c>
       <c r="G19">
-        <v>-10.17940748934363</v>
+        <v>-13.02592972985265</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.521241988878459</v>
       </c>
       <c r="E20">
-        <v>-23.82725431724033</v>
+        <v>-24.88399325351838</v>
       </c>
       <c r="F20">
-        <v>4.390175615537492</v>
+        <v>3.085163952432346</v>
       </c>
       <c r="G20">
-        <v>-9.840697318326363</v>
+        <v>-13.35555189894825</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.277428744448</v>
       </c>
       <c r="E21">
-        <v>-23.9889886726518</v>
+        <v>-26.93253151379946</v>
       </c>
       <c r="F21">
-        <v>4.963178885606383</v>
+        <v>3.567709502115531</v>
       </c>
       <c r="G21">
-        <v>-9.416318174296308</v>
+        <v>-12.56328098623376</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.004228159436817</v>
       </c>
       <c r="E22">
-        <v>-25.24477856809491</v>
+        <v>-26.33620927856925</v>
       </c>
       <c r="F22">
-        <v>4.986187618586542</v>
+        <v>3.663626163685685</v>
       </c>
       <c r="G22">
-        <v>-9.827446484154168</v>
+        <v>-12.08232831228658</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.715413329140175</v>
       </c>
       <c r="E23">
-        <v>-24.9010255731615</v>
+        <v>-27.43559754194196</v>
       </c>
       <c r="F23">
-        <v>4.624906772999177</v>
+        <v>3.252731080875046</v>
       </c>
       <c r="G23">
-        <v>-9.329864672533887</v>
+        <v>-12.12491347268452</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.419787367372187</v>
       </c>
       <c r="E24">
-        <v>-24.50138281342987</v>
+        <v>-27.1732308761299</v>
       </c>
       <c r="F24">
-        <v>5.25335598680705</v>
+        <v>3.59734351758328</v>
       </c>
       <c r="G24">
-        <v>-8.856235137164774</v>
+        <v>-12.08807195038702</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.127412875385518</v>
       </c>
       <c r="E25">
-        <v>-27.11008960435853</v>
+        <v>-28.71978086660726</v>
       </c>
       <c r="F25">
-        <v>4.908872775413653</v>
+        <v>3.737619253573349</v>
       </c>
       <c r="G25">
-        <v>-9.381086176039235</v>
+        <v>-12.26307277107394</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.844544546787307</v>
       </c>
       <c r="E26">
-        <v>-25.46224486627425</v>
+        <v>-28.33680702052784</v>
       </c>
       <c r="F26">
-        <v>5.476354148375482</v>
+        <v>3.709910363949705</v>
       </c>
       <c r="G26">
-        <v>-9.583558556686137</v>
+        <v>-11.93761996109035</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.573817490621412</v>
       </c>
       <c r="E27">
-        <v>-26.1872585076156</v>
+        <v>-29.19004275510061</v>
       </c>
       <c r="F27">
-        <v>4.798754583089904</v>
+        <v>3.536176868560565</v>
       </c>
       <c r="G27">
-        <v>-9.076367899598264</v>
+        <v>-11.6729975000797</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.320276503828575</v>
       </c>
       <c r="E28">
-        <v>-25.61616703118372</v>
+        <v>-29.8053389362683</v>
       </c>
       <c r="F28">
-        <v>4.541486862067655</v>
+        <v>3.308819837718601</v>
       </c>
       <c r="G28">
-        <v>-7.568651149879682</v>
+        <v>-11.21082913346557</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.083763385249388</v>
       </c>
       <c r="E29">
-        <v>-25.2256737960007</v>
+        <v>-29.08121615875613</v>
       </c>
       <c r="F29">
-        <v>4.239464107006956</v>
+        <v>3.599136104642938</v>
       </c>
       <c r="G29">
-        <v>-8.428396756551493</v>
+        <v>-10.71507745380366</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.8705100927689654</v>
       </c>
       <c r="E30">
-        <v>-26.22791429327435</v>
+        <v>-29.58542639661863</v>
       </c>
       <c r="F30">
-        <v>4.107223534824043</v>
+        <v>3.203961778402629</v>
       </c>
       <c r="G30">
-        <v>-8.595685437716259</v>
+        <v>-10.44057985137712</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.6829869535238678</v>
       </c>
       <c r="E31">
-        <v>-26.41217566691169</v>
+        <v>-30.12652338086259</v>
       </c>
       <c r="F31">
-        <v>4.227813947853984</v>
+        <v>3.739386989610923</v>
       </c>
       <c r="G31">
-        <v>-8.615259495288131</v>
+        <v>-9.682046285641295</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.5271117502459894</v>
       </c>
       <c r="E32">
-        <v>-25.65892849498416</v>
+        <v>-28.95502083265121</v>
       </c>
       <c r="F32">
-        <v>5.196342771941971</v>
+        <v>3.162064611903835</v>
       </c>
       <c r="G32">
-        <v>-8.607594349168624</v>
+        <v>-10.22649879490583</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.408690868469764</v>
       </c>
       <c r="E33">
-        <v>-27.65909014975364</v>
+        <v>-29.65675157130557</v>
       </c>
       <c r="F33">
-        <v>4.848138534175199</v>
+        <v>3.224369437737997</v>
       </c>
       <c r="G33">
-        <v>-7.500675192960865</v>
+        <v>-9.932560282881571</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.3322725998208093</v>
       </c>
       <c r="E34">
-        <v>-26.05157724684478</v>
+        <v>-29.42803007043593</v>
       </c>
       <c r="F34">
-        <v>4.310756719161493</v>
+        <v>3.044945058291624</v>
       </c>
       <c r="G34">
-        <v>-8.774273421471364</v>
+        <v>-9.297071109724913</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.3024073504527747</v>
       </c>
       <c r="E35">
-        <v>-24.96360200819269</v>
+        <v>-28.71715811365563</v>
       </c>
       <c r="F35">
-        <v>4.481788080082701</v>
+        <v>3.293278008507277</v>
       </c>
       <c r="G35">
-        <v>-7.751541640720941</v>
+        <v>-9.281495407494331</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.3193293311463338</v>
       </c>
       <c r="E36">
-        <v>-26.16297883421065</v>
+        <v>-28.13628582455379</v>
       </c>
       <c r="F36">
-        <v>3.876345942520182</v>
+        <v>3.202280192574945</v>
       </c>
       <c r="G36">
-        <v>-7.967373201440572</v>
+        <v>-8.928738125204582</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.3838805038582239</v>
       </c>
       <c r="E37">
-        <v>-23.75745544771526</v>
+        <v>-28.21563292691464</v>
       </c>
       <c r="F37">
-        <v>4.923571326608927</v>
+        <v>3.216702069057685</v>
       </c>
       <c r="G37">
-        <v>-8.784279100116805</v>
+        <v>-8.704998619118468</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.4955360309171459</v>
       </c>
       <c r="E38">
-        <v>-24.12064962486019</v>
+        <v>-28.24910781019275</v>
       </c>
       <c r="F38">
-        <v>4.625723543258338</v>
+        <v>3.173527560023774</v>
       </c>
       <c r="G38">
-        <v>-8.370003537654359</v>
+        <v>-8.787398939903186</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.6502818438548024</v>
       </c>
       <c r="E39">
-        <v>-23.48667852897042</v>
+        <v>-27.80470173880213</v>
       </c>
       <c r="F39">
-        <v>4.599739314567323</v>
+        <v>3.596889572246546</v>
       </c>
       <c r="G39">
-        <v>-8.727144260112587</v>
+        <v>-8.628224452927601</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.8459146203081074</v>
       </c>
       <c r="E40">
-        <v>-22.89701389149391</v>
+        <v>-27.13926591391545</v>
       </c>
       <c r="F40">
-        <v>4.639701414813176</v>
+        <v>3.505429527303452</v>
       </c>
       <c r="G40">
-        <v>-8.379834296412195</v>
+        <v>-8.952123869879479</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.075704567615231</v>
       </c>
       <c r="E41">
-        <v>-23.1843081316776</v>
+        <v>-27.10552522511254</v>
       </c>
       <c r="F41">
-        <v>4.680972335555453</v>
+        <v>3.778485931023059</v>
       </c>
       <c r="G41">
-        <v>-8.721433256319527</v>
+        <v>-8.870908827139127</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.336520476512286</v>
       </c>
       <c r="E42">
-        <v>-22.87746887899926</v>
+        <v>-27.28272198628635</v>
       </c>
       <c r="F42">
-        <v>4.681626745803665</v>
+        <v>3.773202603728004</v>
       </c>
       <c r="G42">
-        <v>-8.09050897008043</v>
+        <v>-9.104569162671471</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.62352410281668</v>
       </c>
       <c r="E43">
-        <v>-22.87015092064492</v>
+        <v>-26.20092257287429</v>
       </c>
       <c r="F43">
-        <v>4.783163051834411</v>
+        <v>3.691469248828582</v>
       </c>
       <c r="G43">
-        <v>-8.682684585098222</v>
+        <v>-9.345868536877411</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.930671072876703</v>
       </c>
       <c r="E44">
-        <v>-21.47754178452798</v>
+        <v>-26.45709264738971</v>
       </c>
       <c r="F44">
-        <v>5.048176008072835</v>
+        <v>3.809861174771493</v>
       </c>
       <c r="G44">
-        <v>-8.764621498718018</v>
+        <v>-9.496368824949023</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.254195085261408</v>
       </c>
       <c r="E45">
-        <v>-21.656262774258</v>
+        <v>-26.19451416780008</v>
       </c>
       <c r="F45">
-        <v>4.766222938447162</v>
+        <v>3.915915396617109</v>
       </c>
       <c r="G45">
-        <v>-7.99819695745555</v>
+        <v>-9.423438980168569</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.584447573158621</v>
       </c>
       <c r="E46">
-        <v>-21.83025740950037</v>
+        <v>-25.13075215117174</v>
       </c>
       <c r="F46">
-        <v>4.60346696787992</v>
+        <v>4.075392689004069</v>
       </c>
       <c r="G46">
-        <v>-8.880582941221498</v>
+        <v>-10.13166610837824</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.918156995278964</v>
       </c>
       <c r="E47">
-        <v>-20.48012731881379</v>
+        <v>-24.01457660762407</v>
       </c>
       <c r="F47">
-        <v>4.850100108185028</v>
+        <v>4.042698684350379</v>
       </c>
       <c r="G47">
-        <v>-7.678564802537847</v>
+        <v>-10.30295836637347</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.244881498400407</v>
       </c>
       <c r="E48">
-        <v>-20.91418358758294</v>
+        <v>-24.49200070904709</v>
       </c>
       <c r="F48">
-        <v>4.682927282626061</v>
+        <v>3.731931682985727</v>
       </c>
       <c r="G48">
-        <v>-8.818859717598396</v>
+        <v>-10.82986145049655</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.560865086714305</v>
       </c>
       <c r="E49">
-        <v>-19.52693624728636</v>
+        <v>-24.04109901514443</v>
       </c>
       <c r="F49">
-        <v>4.801358970204306</v>
+        <v>4.022592550749629</v>
       </c>
       <c r="G49">
-        <v>-9.077225529196445</v>
+        <v>-10.30042072263091</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.858728752373931</v>
       </c>
       <c r="E50">
-        <v>-19.37721713223761</v>
+        <v>-23.64037642046834</v>
       </c>
       <c r="F50">
-        <v>5.333025050138695</v>
+        <v>3.868153388906495</v>
       </c>
       <c r="G50">
-        <v>-8.996386433677213</v>
+        <v>-10.45853002581332</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.132999533859386</v>
       </c>
       <c r="E51">
-        <v>-18.6194388067547</v>
+        <v>-23.75554912371716</v>
       </c>
       <c r="F51">
-        <v>4.836145430917468</v>
+        <v>3.891654172123916</v>
       </c>
       <c r="G51">
-        <v>-9.397622632279345</v>
+        <v>-11.05943988686069</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.379969623363198</v>
       </c>
       <c r="E52">
-        <v>-18.34797245492993</v>
+        <v>-22.70555915584196</v>
       </c>
       <c r="F52">
-        <v>4.993492162344428</v>
+        <v>3.9391113406303</v>
       </c>
       <c r="G52">
-        <v>-9.323900426515488</v>
+        <v>-10.89002605959875</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.594493662269992</v>
       </c>
       <c r="E53">
-        <v>-19.27602829151949</v>
+        <v>-22.46280810711706</v>
       </c>
       <c r="F53">
-        <v>4.694837549143512</v>
+        <v>3.75666673363332</v>
       </c>
       <c r="G53">
-        <v>-9.660305310058799</v>
+        <v>-10.9712998440924</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.778313970030859</v>
       </c>
       <c r="E54">
-        <v>-16.77647204741866</v>
+        <v>-22.04572185982115</v>
       </c>
       <c r="F54">
-        <v>4.197568597242968</v>
+        <v>4.131173293173783</v>
       </c>
       <c r="G54">
-        <v>-10.15765476541047</v>
+        <v>-11.19594397317934</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.928299787381216</v>
       </c>
       <c r="E55">
-        <v>-16.65050514793661</v>
+        <v>-21.6843135635459</v>
       </c>
       <c r="F55">
-        <v>4.285411990105439</v>
+        <v>3.848053882244967</v>
       </c>
       <c r="G55">
-        <v>-10.49260024272735</v>
+        <v>-11.58203524240842</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.050806615954064</v>
       </c>
       <c r="E56">
-        <v>-17.91109615567122</v>
+        <v>-20.20557097776334</v>
       </c>
       <c r="F56">
-        <v>4.532018622653657</v>
+        <v>3.972554189416122</v>
       </c>
       <c r="G56">
-        <v>-10.55560925806157</v>
+        <v>-11.2837080687265</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.147290375549327</v>
       </c>
       <c r="E57">
-        <v>-17.41407720321766</v>
+        <v>-20.99363452022691</v>
       </c>
       <c r="F57">
-        <v>4.347473275923178</v>
+        <v>4.08242055804942</v>
       </c>
       <c r="G57">
-        <v>-10.94898450469986</v>
+        <v>-11.33480947798065</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.224549436763115</v>
       </c>
       <c r="E58">
-        <v>-16.85710249207888</v>
+        <v>-20.62372044715841</v>
       </c>
       <c r="F58">
-        <v>4.344250926726288</v>
+        <v>4.305953844960061</v>
       </c>
       <c r="G58">
-        <v>-10.0002085913542</v>
+        <v>-11.42538665082474</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.287332378964943</v>
       </c>
       <c r="E59">
-        <v>-17.34927880012768</v>
+        <v>-19.88111380264509</v>
       </c>
       <c r="F59">
-        <v>4.184412466151707</v>
+        <v>4.166731792306354</v>
       </c>
       <c r="G59">
-        <v>-10.27627916739689</v>
+        <v>-11.24123517034597</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.342211097025504</v>
       </c>
       <c r="E60">
-        <v>-17.6039246460869</v>
+        <v>-20.14693594027942</v>
       </c>
       <c r="F60">
-        <v>4.913561334913498</v>
+        <v>4.295751672027182</v>
       </c>
       <c r="G60">
-        <v>-10.96327310984703</v>
+        <v>-12.00221761450826</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.395551566142817</v>
       </c>
       <c r="E61">
-        <v>-15.56327748732299</v>
+        <v>-19.79857703398677</v>
       </c>
       <c r="F61">
-        <v>4.642981749728262</v>
+        <v>4.463047095961765</v>
       </c>
       <c r="G61">
-        <v>-10.44249874865159</v>
+        <v>-11.73358635517796</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.450027816694725</v>
       </c>
       <c r="E62">
-        <v>-15.19584288141541</v>
+        <v>-19.75542932153313</v>
       </c>
       <c r="F62">
-        <v>4.454635853353738</v>
+        <v>4.123804136758478</v>
       </c>
       <c r="G62">
-        <v>-11.01041924104565</v>
+        <v>-12.08272906158131</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.511158752332159</v>
       </c>
       <c r="E63">
-        <v>-14.52061793743611</v>
+        <v>-18.90025819048298</v>
       </c>
       <c r="F63">
-        <v>4.958306428543117</v>
+        <v>4.272916896201611</v>
       </c>
       <c r="G63">
-        <v>-11.41800868661025</v>
+        <v>-11.90177182710977</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.577167272819385</v>
       </c>
       <c r="E64">
-        <v>-15.04566275990961</v>
+        <v>-19.3678973260247</v>
       </c>
       <c r="F64">
-        <v>4.261099406833273</v>
+        <v>4.071573915277163</v>
       </c>
       <c r="G64">
-        <v>-11.65553422950974</v>
+        <v>-12.36543223425772</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.649979895913475</v>
       </c>
       <c r="E65">
-        <v>-13.54144022264924</v>
+        <v>-18.46482305555398</v>
       </c>
       <c r="F65">
-        <v>5.089052625931379</v>
+        <v>4.140229005621187</v>
       </c>
       <c r="G65">
-        <v>-10.423283668461</v>
+        <v>-11.90957534269261</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.725454557817359</v>
       </c>
       <c r="E66">
-        <v>-14.46538438002722</v>
+        <v>-19.03213095646894</v>
       </c>
       <c r="F66">
-        <v>4.639500949901699</v>
+        <v>4.542880176039165</v>
       </c>
       <c r="G66">
-        <v>-10.68530713323119</v>
+        <v>-12.8547588714809</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.802536423504312</v>
       </c>
       <c r="E67">
-        <v>-15.07198166007505</v>
+        <v>-19.60590540741665</v>
       </c>
       <c r="F67">
-        <v>4.733169422340656</v>
+        <v>4.174952510411736</v>
       </c>
       <c r="G67">
-        <v>-11.28962793208685</v>
+        <v>-12.26855011322609</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.87730850182569</v>
       </c>
       <c r="E68">
-        <v>-14.62691107487245</v>
+        <v>-19.26020040316057</v>
       </c>
       <c r="F68">
-        <v>3.85196046291657</v>
+        <v>4.267055368459402</v>
       </c>
       <c r="G68">
-        <v>-11.05690354849042</v>
+        <v>-12.62520393181808</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.947861138848326</v>
       </c>
       <c r="E69">
-        <v>-13.15137061502134</v>
+        <v>-19.30182804026933</v>
       </c>
       <c r="F69">
-        <v>4.617787783539518</v>
+        <v>4.77300726747609</v>
       </c>
       <c r="G69">
-        <v>-11.59418956385235</v>
+        <v>-12.4597989028758</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.014401485625599</v>
       </c>
       <c r="E70">
-        <v>-15.81988780223885</v>
+        <v>-18.67979327372711</v>
       </c>
       <c r="F70">
-        <v>4.791947059773698</v>
+        <v>4.61010384751115</v>
       </c>
       <c r="G70">
-        <v>-10.97961898173199</v>
+        <v>-12.7772001765404</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.073365470055389</v>
       </c>
       <c r="E71">
-        <v>-15.22553834238794</v>
+        <v>-18.60139725675964</v>
       </c>
       <c r="F71">
-        <v>4.627221231522599</v>
+        <v>4.537127992794125</v>
       </c>
       <c r="G71">
-        <v>-10.63759316508401</v>
+        <v>-13.10320124288813</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.127771925291328</v>
       </c>
       <c r="E72">
-        <v>-16.71285730955626</v>
+        <v>-18.73734016984393</v>
       </c>
       <c r="F72">
-        <v>4.892678192688923</v>
+        <v>4.128230932159038</v>
       </c>
       <c r="G72">
-        <v>-10.93283574403153</v>
+        <v>-12.95223754765159</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.175199508357924</v>
       </c>
       <c r="E73">
-        <v>-17.1496713106451</v>
+        <v>-18.75079657453638</v>
       </c>
       <c r="F73">
-        <v>4.324835651539473</v>
+        <v>4.655564650576787</v>
       </c>
       <c r="G73">
-        <v>-10.72628538033331</v>
+        <v>-12.74309471457439</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.218284945146546</v>
       </c>
       <c r="E74">
-        <v>-15.89398109227379</v>
+        <v>-18.71638721871017</v>
       </c>
       <c r="F74">
-        <v>4.561274902585731</v>
+        <v>4.481899081314676</v>
       </c>
       <c r="G74">
-        <v>-11.70217779237457</v>
+        <v>-12.80838160456436</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.255091220567908</v>
       </c>
       <c r="E75">
-        <v>-15.97391379743144</v>
+        <v>-19.05900223374058</v>
       </c>
       <c r="F75">
-        <v>4.14428966262971</v>
+        <v>4.545184694153753</v>
       </c>
       <c r="G75">
-        <v>-10.32682970954232</v>
+        <v>-13.05950912678355</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.288289102680182</v>
       </c>
       <c r="E76">
-        <v>-17.3131998533489</v>
+        <v>-19.49163395102532</v>
       </c>
       <c r="F76">
-        <v>4.633392568673456</v>
+        <v>4.587134876166325</v>
       </c>
       <c r="G76">
-        <v>-11.1290906364347</v>
+        <v>-13.22422230840918</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.319693809060126</v>
       </c>
       <c r="E77">
-        <v>-16.85704019390901</v>
+        <v>-20.25368177775016</v>
       </c>
       <c r="F77">
-        <v>3.953001405240442</v>
+        <v>4.602050459621133</v>
       </c>
       <c r="G77">
-        <v>-10.65436589370962</v>
+        <v>-12.48901835633954</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.349473184976668</v>
       </c>
       <c r="E78">
-        <v>-17.64983009086023</v>
+        <v>-20.40470084794357</v>
       </c>
       <c r="F78">
-        <v>4.281493812290197</v>
+        <v>4.345839735404858</v>
       </c>
       <c r="G78">
-        <v>-10.58569025724038</v>
+        <v>-12.42590491122168</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.382994700831314</v>
       </c>
       <c r="E79">
-        <v>-16.81448223746349</v>
+        <v>-19.63870747046015</v>
       </c>
       <c r="F79">
-        <v>4.441507886754172</v>
+        <v>4.711959903359377</v>
       </c>
       <c r="G79">
-        <v>-9.697845206534417</v>
+        <v>-12.48807326679756</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.419005127800927</v>
       </c>
       <c r="E80">
-        <v>-18.09877146901757</v>
+        <v>-20.91608991158104</v>
       </c>
       <c r="F80">
-        <v>4.346800641592105</v>
+        <v>4.399673676177992</v>
       </c>
       <c r="G80">
-        <v>-10.70525061116271</v>
+        <v>-12.50775697564226</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.461534706440854</v>
       </c>
       <c r="E81">
-        <v>-18.3807371390715</v>
+        <v>-20.61528527495768</v>
       </c>
       <c r="F81">
-        <v>5.129713868265196</v>
+        <v>4.53477708610498</v>
       </c>
       <c r="G81">
-        <v>-10.56050179342532</v>
+        <v>-12.51597690498738</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.508793742030511</v>
       </c>
       <c r="E82">
-        <v>-19.55786936523368</v>
+        <v>-21.98494791850494</v>
       </c>
       <c r="F82">
-        <v>4.030897762330096</v>
+        <v>4.429751696573642</v>
       </c>
       <c r="G82">
-        <v>-10.1567658068772</v>
+        <v>-12.28027366181249</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.563159824269541</v>
       </c>
       <c r="E83">
-        <v>-18.92795595680826</v>
+        <v>-22.58587606509438</v>
       </c>
       <c r="F83">
-        <v>4.230118465968572</v>
+        <v>4.965915811505233</v>
       </c>
       <c r="G83">
-        <v>-9.617670545513624</v>
+        <v>-12.08022666289073</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.622599493490197</v>
       </c>
       <c r="E84">
-        <v>-22.33718177096364</v>
+        <v>-24.06004181199697</v>
       </c>
       <c r="F84">
-        <v>4.555975007942619</v>
+        <v>4.115704360293904</v>
       </c>
       <c r="G84">
-        <v>-9.430281741741878</v>
+        <v>-11.75098174638855</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.684967852832853</v>
       </c>
       <c r="E85">
-        <v>-21.94002263160426</v>
+        <v>-25.02337502557963</v>
       </c>
       <c r="F85">
-        <v>4.488708261365688</v>
+        <v>4.548822883786849</v>
       </c>
       <c r="G85">
-        <v>-10.31580322976175</v>
+        <v>-12.08846486744799</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.748454697744047</v>
       </c>
       <c r="E86">
-        <v>-23.47580126851069</v>
+        <v>-25.35157424410155</v>
       </c>
       <c r="F86">
-        <v>4.549386173620752</v>
+        <v>5.162856848051204</v>
       </c>
       <c r="G86">
-        <v>-10.09432462849154</v>
+        <v>-11.27115952484931</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.806227944315811</v>
       </c>
       <c r="E87">
-        <v>-24.76114541574128</v>
+        <v>-26.77233384657817</v>
       </c>
       <c r="F87">
-        <v>4.474006396700802</v>
+        <v>4.591858227097088</v>
       </c>
       <c r="G87">
-        <v>-9.949018416783948</v>
+        <v>-11.40672243774287</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.854932459739231</v>
       </c>
       <c r="E88">
-        <v>-27.06024276203793</v>
+        <v>-28.21507639659711</v>
       </c>
       <c r="F88">
-        <v>4.588968881596124</v>
+        <v>5.230242879534138</v>
       </c>
       <c r="G88">
-        <v>-9.43919090765905</v>
+        <v>-11.53462281526151</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.88485032123688</v>
       </c>
       <c r="E89">
-        <v>-26.57283849380136</v>
+        <v>-29.01947451920123</v>
       </c>
       <c r="F89">
-        <v>4.462717405735451</v>
+        <v>5.184392743789186</v>
       </c>
       <c r="G89">
-        <v>-9.266901345230007</v>
+        <v>-11.50732748056142</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.89021468986707</v>
       </c>
       <c r="E90">
-        <v>-30.29853901090867</v>
+        <v>-30.28844047757235</v>
       </c>
       <c r="F90">
-        <v>4.647648771675635</v>
+        <v>5.355611315743427</v>
       </c>
       <c r="G90">
-        <v>-8.770292035969916</v>
+        <v>-11.01815226652452</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.858317721050132</v>
       </c>
       <c r="E91">
-        <v>-30.15977399072916</v>
+        <v>-31.8064828255161</v>
       </c>
       <c r="F91">
-        <v>4.585165018482468</v>
+        <v>4.953258357590457</v>
       </c>
       <c r="G91">
-        <v>-8.13807804190281</v>
+        <v>-10.68576792965153</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.783108904001111</v>
       </c>
       <c r="E92">
-        <v>-32.63194603595974</v>
+        <v>-33.64503679781951</v>
       </c>
       <c r="F92">
-        <v>4.117251750602334</v>
+        <v>5.195045548589188</v>
       </c>
       <c r="G92">
-        <v>-8.749449156526763</v>
+        <v>-10.75987783098716</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.655220592814143</v>
       </c>
       <c r="E93">
-        <v>-33.92026180589324</v>
+        <v>-35.34059570420907</v>
       </c>
       <c r="F93">
-        <v>4.905728292752626</v>
+        <v>5.714725152205069</v>
       </c>
       <c r="G93">
-        <v>-8.672331677422163</v>
+        <v>-10.99666583853966</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.469538724745499</v>
       </c>
       <c r="E94">
-        <v>-36.24053430012954</v>
+        <v>-37.93637354828353</v>
       </c>
       <c r="F94">
-        <v>4.35369928532262</v>
+        <v>5.366802559355248</v>
       </c>
       <c r="G94">
-        <v>-8.874609557597029</v>
+        <v>-10.66451646867987</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.226249168521794</v>
       </c>
       <c r="E95">
-        <v>-37.04037012009334</v>
+        <v>-39.90491888184275</v>
       </c>
       <c r="F95">
-        <v>4.733358290108495</v>
+        <v>5.254948108955231</v>
       </c>
       <c r="G95">
-        <v>-8.270558970806558</v>
+        <v>-10.76506146437282</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.925240246919037</v>
       </c>
       <c r="E96">
-        <v>-41.34696161575346</v>
+        <v>-41.53323729688334</v>
       </c>
       <c r="F96">
-        <v>4.390106032675657</v>
+        <v>5.653540279099492</v>
       </c>
       <c r="G96">
-        <v>-7.95422418630743</v>
+        <v>-10.64606372590988</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.578950074678105</v>
       </c>
       <c r="E97">
-        <v>-42.24542374504795</v>
+        <v>-45.28994984295316</v>
       </c>
       <c r="F97">
-        <v>4.04072551319691</v>
+        <v>5.544530442360688</v>
       </c>
       <c r="G97">
-        <v>-8.145886778974829</v>
+        <v>-10.7226760259361</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.191072271770195</v>
       </c>
       <c r="E98">
-        <v>-44.72381522423746</v>
+        <v>-46.5285163710322</v>
       </c>
       <c r="F98">
-        <v>4.144781712866973</v>
+        <v>5.320834795439098</v>
       </c>
       <c r="G98">
-        <v>-9.059588644111178</v>
+        <v>-10.59514767952169</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.78887890733672</v>
       </c>
       <c r="E99">
-        <v>-47.52743533754882</v>
+        <v>-48.31968635533064</v>
       </c>
       <c r="F99">
-        <v>4.348420928231981</v>
+        <v>5.511377522165846</v>
       </c>
       <c r="G99">
-        <v>-8.457041846205188</v>
+        <v>-10.48735003535462</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.377692685538286</v>
       </c>
       <c r="E100">
-        <v>-48.61523302641676</v>
+        <v>-50.75088281763045</v>
       </c>
       <c r="F100">
-        <v>4.022342383793983</v>
+        <v>5.318124377297138</v>
       </c>
       <c r="G100">
-        <v>-8.178031571752912</v>
+        <v>-10.11892306402901</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.999461532429215</v>
       </c>
       <c r="E101">
-        <v>-51.98249479334608</v>
+        <v>-52.60748249314025</v>
       </c>
       <c r="F101">
-        <v>3.277429683356917</v>
+        <v>5.682055998573461</v>
       </c>
       <c r="G101">
-        <v>-9.016225481825083</v>
+        <v>-10.25153583553461</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.646004519181425</v>
       </c>
       <c r="E102">
-        <v>-53.17633538866804</v>
+        <v>-54.43471792628067</v>
       </c>
       <c r="F102">
-        <v>3.348003272605823</v>
+        <v>5.434173680224932</v>
       </c>
       <c r="G102">
-        <v>-8.427003924312135</v>
+        <v>-10.4697000965464</v>
       </c>
     </row>
   </sheetData>
